--- a/data/trans_orig/P57B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat) en 2023</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) en 2023 (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>49309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373141</t>
+          <t>371979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393753</t>
+          <t>393773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273368</t>
+          <t>274403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298357</t>
+          <t>298949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659312</t>
+          <t>659339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689433</t>
+          <t>690288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43248</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72245</t>
+          <t>74501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382939</t>
+          <t>384453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408150</t>
+          <t>407620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464859</t>
+          <t>463249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490497</t>
+          <t>489569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>857744</t>
+          <t>855488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892244</t>
+          <t>891356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52458</t>
+          <t>51683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70751</t>
+          <t>70197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102309</t>
+          <t>102554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475625</t>
+          <t>476080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500564</t>
+          <t>500552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>486084</t>
+          <t>486859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505398</t>
+          <t>505396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>967859</t>
+          <t>967614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999417</t>
+          <t>999971</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>30518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97501</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>65859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93770</t>
+          <t>94227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87604</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178712</t>
+          <t>179848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>781993</t>
+          <t>782122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>850978</t>
+          <t>848976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606486</t>
+          <t>606029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635697</t>
+          <t>634397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1401038</t>
+          <t>1399902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1492146</t>
+          <t>1491176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68929</t>
+          <t>68596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99380</t>
+          <t>98529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88140</t>
+          <t>87511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113643</t>
+          <t>115009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161909</t>
+          <t>164641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202783</t>
+          <t>206404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>453925</t>
+          <t>454776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484376</t>
+          <t>484709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>421678</t>
+          <t>420312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>447181</t>
+          <t>447810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>885842</t>
+          <t>882221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>926716</t>
+          <t>923984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36616</t>
+          <t>36545</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56611</t>
+          <t>56697</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>29149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116356</t>
+          <t>116511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63868</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158408</t>
+          <t>157190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>305702</t>
+          <t>305616</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>325697</t>
+          <t>325768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>483154</t>
+          <t>482999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>571582</t>
+          <t>570361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>803415</t>
+          <t>804633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>897955</t>
+          <t>906159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44225</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>64990</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125227</t>
+          <t>123775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151135</t>
+          <t>150670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>175215</t>
+          <t>173506</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208921</t>
+          <t>208004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208404</t>
+          <t>207332</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228097</t>
+          <t>226562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>256397</t>
+          <t>256862</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>282305</t>
+          <t>283757</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>470933</t>
+          <t>471850</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>504639</t>
+          <t>506348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>254253</t>
+          <t>254826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>365385</t>
+          <t>366914</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>397967</t>
+          <t>397866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>539590</t>
+          <t>534397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>691136</t>
+          <t>704388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>875819</t>
+          <t>881414</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3051168</t>
+          <t>3049639</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3162300</t>
+          <t>3161727</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3062715</t>
+          <t>3067908</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3204338</t>
+          <t>3204439</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6143039</t>
+          <t>6137444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6327722</t>
+          <t>6314470</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>37487</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>387884</t>
+          <t>391394</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371979</t>
+          <t>377494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393773</t>
+          <t>397213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289413</t>
+          <t>331520</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274403</t>
+          <t>313264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298949</t>
+          <t>342723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>677297</t>
+          <t>722915</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659339</t>
+          <t>703218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690288</t>
+          <t>737696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>395610</t>
+          <t>399604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395610</t>
+          <t>399604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>395610</t>
+          <t>399604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313038</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313038</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313038</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>708648</t>
+          <t>760402</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>708648</t>
+          <t>760402</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>708648</t>
+          <t>760402</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37429</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18538</t>
+          <t>23389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44858</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54694</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>46894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74501</t>
+          <t>83597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>397542</t>
+          <t>446280</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384453</t>
+          <t>430934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407620</t>
+          <t>457682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>477752</t>
+          <t>462997</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463249</t>
+          <t>450544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489569</t>
+          <t>473593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>875295</t>
+          <t>909277</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>855488</t>
+          <t>888782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891356</t>
+          <t>925485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>508107</t>
+          <t>496982</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>508107</t>
+          <t>496982</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>508107</t>
+          <t>496982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>929989</t>
+          <t>972379</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>929989</t>
+          <t>972379</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>929989</t>
+          <t>972379</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,102 +1411,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>49246</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55546</t>
+          <t>63848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>49612</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39034</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62842</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>98858</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>83322</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>118042</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>8,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42122</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33146</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51683</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>84697</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>70197</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>102554</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1524,102 +1524,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>489050</t>
+          <t>567040</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476080</t>
+          <t>552438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500552</t>
+          <t>579580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>567832</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>554602</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>578410</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1134872</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1115688</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1150408</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>91,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>496420</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>486859</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>505396</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>985471</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>967614</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>999971</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>531626</t>
+          <t>616286</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>531626</t>
+          <t>616286</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>531626</t>
+          <t>616286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>538542</t>
+          <t>617444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>538542</t>
+          <t>617444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>538542</t>
+          <t>617444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1070168</t>
+          <t>1233730</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1070168</t>
+          <t>1233730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1070168</t>
+          <t>1233730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64979</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>55227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97372</t>
+          <t>85861</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79530</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>74054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94227</t>
+          <t>100571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>144509</t>
+          <t>157460</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179848</t>
+          <t>181996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>814515</t>
+          <t>621821</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>782122</t>
+          <t>605963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848976</t>
+          <t>636597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>620726</t>
+          <t>635927</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606029</t>
+          <t>622813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>634397</t>
+          <t>649330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1435241</t>
+          <t>1257748</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1399902</t>
+          <t>1233212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1491176</t>
+          <t>1275674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>879494</t>
+          <t>691824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>879494</t>
+          <t>691824</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>879494</t>
+          <t>691824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700256</t>
+          <t>723384</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700256</t>
+          <t>723384</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700256</t>
+          <t>723384</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1579750</t>
+          <t>1415208</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1579750</t>
+          <t>1415208</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1579750</t>
+          <t>1415208</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>90826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68596</t>
+          <t>74939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98529</t>
+          <t>107883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100306</t>
+          <t>110434</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87511</t>
+          <t>96196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115009</t>
+          <t>126321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>183978</t>
+          <t>201260</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164641</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206404</t>
+          <t>223355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -2210,17 +2210,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>469632</t>
+          <t>509891</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454776</t>
+          <t>492834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484709</t>
+          <t>525778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>435015</t>
+          <t>484386</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>420312</t>
+          <t>468499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>447810</t>
+          <t>498624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>904647</t>
+          <t>994277</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>882221</t>
+          <t>972182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>923984</t>
+          <t>1015783</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>553305</t>
+          <t>600717</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>553305</t>
+          <t>600717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>553305</t>
+          <t>600717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>535321</t>
+          <t>594820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>535321</t>
+          <t>594820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>535321</t>
+          <t>594820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1088625</t>
+          <t>1195537</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1088625</t>
+          <t>1195537</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1088625</t>
+          <t>1195537</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46254</t>
+          <t>50214</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>39484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56697</t>
+          <t>61845</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73323</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>68343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116511</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>119577</t>
+          <t>130384</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>117295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157190</t>
+          <t>147779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>316059</t>
+          <t>350592</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>305616</t>
+          <t>338961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>325768</t>
+          <t>361322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>526187</t>
+          <t>351734</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>482999</t>
+          <t>339995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>570361</t>
+          <t>363561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>842246</t>
+          <t>702326</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>804633</t>
+          <t>684931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>906159</t>
+          <t>715415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>362313</t>
+          <t>400806</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>362313</t>
+          <t>400806</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>362313</t>
+          <t>400806</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599510</t>
+          <t>431904</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599510</t>
+          <t>431904</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599510</t>
+          <t>431904</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>961823</t>
+          <t>832710</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>961823</t>
+          <t>832710</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>961823</t>
+          <t>832710</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>54081</t>
+          <t>58295</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45760</t>
+          <t>47657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64990</t>
+          <t>69758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>138222</t>
+          <t>150597</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123775</t>
+          <t>137185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150670</t>
+          <t>166457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>192303</t>
+          <t>208892</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173506</t>
+          <t>187193</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208004</t>
+          <t>226947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>218241</t>
+          <t>240571</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207332</t>
+          <t>229108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226562</t>
+          <t>251209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>269310</t>
+          <t>294695</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>256862</t>
+          <t>278835</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>283757</t>
+          <t>308107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>487551</t>
+          <t>535266</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>471850</t>
+          <t>517211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>506348</t>
+          <t>556965</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>272322</t>
+          <t>298866</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>272322</t>
+          <t>298866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>272322</t>
+          <t>298866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>407532</t>
+          <t>445292</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>407532</t>
+          <t>445292</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>407532</t>
+          <t>445292</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>679854</t>
+          <t>744158</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>679854</t>
+          <t>744158</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>679854</t>
+          <t>744158</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>323628</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>254826</t>
+          <t>321937</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>366914</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>397866</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>534397</t>
+          <t>575781</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>811110</t>
+          <t>897443</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>704388</t>
+          <t>850906</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>881414</t>
+          <t>949298</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3092925</t>
+          <t>3127590</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3049639</t>
+          <t>3089614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3161727</t>
+          <t>3161564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3114823</t>
+          <t>3129091</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3067908</t>
+          <t>3094842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3204439</t>
+          <t>3165103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6207748</t>
+          <t>6256681</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6137444</t>
+          <t>6204826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6314470</t>
+          <t>6303218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
